--- a/Assets/Resources/VNovelizerRes/ExcelVNScripts/sntzm_final(2).xlsx
+++ b/Assets/Resources/VNovelizerRes/ExcelVNScripts/sntzm_final(2).xlsx
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1468" uniqueCount="495">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1468" uniqueCount="494">
   <si>
     <t>ID</t>
   </si>
@@ -502,11 +502,6 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
       <t>loadScript(</t>
     </r>
     <r>
@@ -515,7 +510,7 @@
         <rFont val="宋体"/>
         <charset val="134"/>
       </rPr>
-      <t>终局（终）</t>
+      <t>sntzm_final(4)</t>
     </r>
     <r>
       <rPr>
@@ -523,7 +518,7 @@
         <rFont val="Calibri"/>
         <charset val="134"/>
       </rPr>
-      <t>_2, 2)</t>
+      <t>, 2)</t>
     </r>
   </si>
   <si>
@@ -713,9 +708,6 @@
     <t>30</t>
   </si>
   <si>
-    <t>loadScript(终局（终 _2, 1)</t>
-  </si>
-  <si>
     <t>源类型=type:txt_pb; 层级=25; gotomainline=终局（终)_2</t>
   </si>
   <si>
@@ -1008,6 +1000,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
       <t>loadScript(</t>
     </r>
     <r>
@@ -5377,34 +5374,34 @@
       <c r="J69" t="s">
         <v>15</v>
       </c>
-      <c r="K69" t="s">
+      <c r="K69" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="L69" t="s">
         <v>218</v>
-      </c>
-      <c r="L69" t="s">
-        <v>219</v>
       </c>
     </row>
     <row r="70" spans="1:12">
       <c r="A70" t="s">
+        <v>219</v>
+      </c>
+      <c r="B70" t="s">
         <v>220</v>
       </c>
-      <c r="B70" t="s">
+      <c r="C70" t="s">
+        <v>14</v>
+      </c>
+      <c r="D70" t="s">
         <v>221</v>
       </c>
-      <c r="C70" t="s">
-        <v>14</v>
-      </c>
-      <c r="D70" t="s">
+      <c r="E70" t="s">
+        <v>15</v>
+      </c>
+      <c r="F70" t="s">
+        <v>15</v>
+      </c>
+      <c r="G70" t="s">
         <v>222</v>
-      </c>
-      <c r="E70" t="s">
-        <v>15</v>
-      </c>
-      <c r="F70" t="s">
-        <v>15</v>
-      </c>
-      <c r="G70" t="s">
-        <v>223</v>
       </c>
       <c r="H70" t="s">
         <v>15</v>
@@ -5419,12 +5416,12 @@
         <v>31</v>
       </c>
       <c r="L70" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="71" ht="27" spans="1:12">
       <c r="A71" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B71" t="s">
         <v>13</v>
@@ -5433,7 +5430,7 @@
         <v>14</v>
       </c>
       <c r="D71" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="E71" t="s">
         <v>15</v>
@@ -5442,7 +5439,7 @@
         <v>15</v>
       </c>
       <c r="G71" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="H71" t="s">
         <v>15</v>
@@ -5462,7 +5459,7 @@
     </row>
     <row r="72" spans="1:12">
       <c r="A72" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B72" t="s">
         <v>13</v>
@@ -5480,7 +5477,7 @@
         <v>15</v>
       </c>
       <c r="G72" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="H72" t="s">
         <v>15</v>
@@ -5500,7 +5497,7 @@
     </row>
     <row r="73" ht="27" spans="1:12">
       <c r="A73" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B73" t="s">
         <v>13</v>
@@ -5518,7 +5515,7 @@
         <v>15</v>
       </c>
       <c r="G73" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="H73" t="s">
         <v>15</v>
@@ -5538,7 +5535,7 @@
     </row>
     <row r="74" spans="1:12">
       <c r="A74" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B74" t="s">
         <v>28</v>
@@ -5556,27 +5553,27 @@
         <v>15</v>
       </c>
       <c r="G74" t="s">
+        <v>231</v>
+      </c>
+      <c r="H74" t="s">
+        <v>15</v>
+      </c>
+      <c r="I74" t="s">
+        <v>15</v>
+      </c>
+      <c r="J74" t="s">
+        <v>15</v>
+      </c>
+      <c r="K74" t="s">
+        <v>15</v>
+      </c>
+      <c r="L74" t="s">
         <v>232</v>
-      </c>
-      <c r="H74" t="s">
-        <v>15</v>
-      </c>
-      <c r="I74" t="s">
-        <v>15</v>
-      </c>
-      <c r="J74" t="s">
-        <v>15</v>
-      </c>
-      <c r="K74" t="s">
-        <v>15</v>
-      </c>
-      <c r="L74" t="s">
-        <v>233</v>
       </c>
     </row>
     <row r="75" ht="27" spans="1:12">
       <c r="A75" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B75" t="s">
         <v>13</v>
@@ -5594,19 +5591,19 @@
         <v>15</v>
       </c>
       <c r="G75" t="s">
+        <v>234</v>
+      </c>
+      <c r="H75" t="s">
+        <v>15</v>
+      </c>
+      <c r="I75" t="s">
+        <v>15</v>
+      </c>
+      <c r="J75" t="s">
+        <v>15</v>
+      </c>
+      <c r="K75" t="s">
         <v>235</v>
-      </c>
-      <c r="H75" t="s">
-        <v>15</v>
-      </c>
-      <c r="I75" t="s">
-        <v>15</v>
-      </c>
-      <c r="J75" t="s">
-        <v>15</v>
-      </c>
-      <c r="K75" t="s">
-        <v>236</v>
       </c>
       <c r="L75" t="s">
         <v>39</v>
@@ -5614,7 +5611,7 @@
     </row>
     <row r="76" spans="1:12">
       <c r="A76" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B76" t="s">
         <v>28</v>
@@ -5632,7 +5629,7 @@
         <v>15</v>
       </c>
       <c r="G76" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="H76" t="s">
         <v>15</v>
@@ -5652,7 +5649,7 @@
     </row>
     <row r="77" ht="42" spans="1:12">
       <c r="A77" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B77" t="s">
         <v>28</v>
@@ -5670,7 +5667,7 @@
         <v>15</v>
       </c>
       <c r="G77" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="H77" t="s">
         <v>15</v>
@@ -5690,7 +5687,7 @@
     </row>
     <row r="78" spans="1:12">
       <c r="A78" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B78" t="s">
         <v>13</v>
@@ -5708,19 +5705,19 @@
         <v>15</v>
       </c>
       <c r="G78" t="s">
+        <v>241</v>
+      </c>
+      <c r="H78" t="s">
+        <v>15</v>
+      </c>
+      <c r="I78" t="s">
+        <v>15</v>
+      </c>
+      <c r="J78" t="s">
+        <v>15</v>
+      </c>
+      <c r="K78" t="s">
         <v>242</v>
-      </c>
-      <c r="H78" t="s">
-        <v>15</v>
-      </c>
-      <c r="I78" t="s">
-        <v>15</v>
-      </c>
-      <c r="J78" t="s">
-        <v>15</v>
-      </c>
-      <c r="K78" t="s">
-        <v>243</v>
       </c>
       <c r="L78" t="s">
         <v>48</v>
@@ -5728,7 +5725,7 @@
     </row>
     <row r="79" ht="43.5" spans="1:12">
       <c r="A79" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B79" t="s">
         <v>28</v>
@@ -5746,7 +5743,7 @@
         <v>15</v>
       </c>
       <c r="G79" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="H79" t="s">
         <v>15</v>
@@ -5761,12 +5758,12 @@
         <v>31</v>
       </c>
       <c r="L79" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="80" ht="30" spans="1:12">
       <c r="A80" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B80" t="s">
         <v>28</v>
@@ -5784,27 +5781,27 @@
         <v>15</v>
       </c>
       <c r="G80" t="s">
+        <v>247</v>
+      </c>
+      <c r="H80" t="s">
+        <v>15</v>
+      </c>
+      <c r="I80" t="s">
+        <v>15</v>
+      </c>
+      <c r="J80" t="s">
+        <v>15</v>
+      </c>
+      <c r="K80" t="s">
+        <v>15</v>
+      </c>
+      <c r="L80" t="s">
         <v>248</v>
-      </c>
-      <c r="H80" t="s">
-        <v>15</v>
-      </c>
-      <c r="I80" t="s">
-        <v>15</v>
-      </c>
-      <c r="J80" t="s">
-        <v>15</v>
-      </c>
-      <c r="K80" t="s">
-        <v>15</v>
-      </c>
-      <c r="L80" t="s">
-        <v>249</v>
       </c>
     </row>
     <row r="81" ht="54" spans="1:12">
       <c r="A81" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B81" t="s">
         <v>28</v>
@@ -5822,27 +5819,27 @@
         <v>15</v>
       </c>
       <c r="G81" t="s">
+        <v>250</v>
+      </c>
+      <c r="H81" t="s">
+        <v>15</v>
+      </c>
+      <c r="I81" t="s">
+        <v>15</v>
+      </c>
+      <c r="J81" t="s">
+        <v>15</v>
+      </c>
+      <c r="K81" t="s">
+        <v>15</v>
+      </c>
+      <c r="L81" t="s">
         <v>251</v>
-      </c>
-      <c r="H81" t="s">
-        <v>15</v>
-      </c>
-      <c r="I81" t="s">
-        <v>15</v>
-      </c>
-      <c r="J81" t="s">
-        <v>15</v>
-      </c>
-      <c r="K81" t="s">
-        <v>15</v>
-      </c>
-      <c r="L81" t="s">
-        <v>252</v>
       </c>
     </row>
     <row r="82" ht="58.5" spans="1:12">
       <c r="A82" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B82" t="s">
         <v>28</v>
@@ -5860,27 +5857,27 @@
         <v>15</v>
       </c>
       <c r="G82" t="s">
+        <v>253</v>
+      </c>
+      <c r="H82" t="s">
+        <v>15</v>
+      </c>
+      <c r="I82" t="s">
+        <v>15</v>
+      </c>
+      <c r="J82" t="s">
+        <v>15</v>
+      </c>
+      <c r="K82" t="s">
+        <v>15</v>
+      </c>
+      <c r="L82" t="s">
         <v>254</v>
-      </c>
-      <c r="H82" t="s">
-        <v>15</v>
-      </c>
-      <c r="I82" t="s">
-        <v>15</v>
-      </c>
-      <c r="J82" t="s">
-        <v>15</v>
-      </c>
-      <c r="K82" t="s">
-        <v>15</v>
-      </c>
-      <c r="L82" t="s">
-        <v>255</v>
       </c>
     </row>
     <row r="83" ht="42" spans="1:12">
       <c r="A83" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B83" t="s">
         <v>28</v>
@@ -5898,7 +5895,7 @@
         <v>15</v>
       </c>
       <c r="G83" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H83" t="s">
         <v>15</v>
@@ -5918,7 +5915,7 @@
     </row>
     <row r="84" ht="30" spans="1:12">
       <c r="A84" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B84" t="s">
         <v>13</v>
@@ -5936,19 +5933,19 @@
         <v>15</v>
       </c>
       <c r="G84" t="s">
+        <v>258</v>
+      </c>
+      <c r="H84" t="s">
+        <v>15</v>
+      </c>
+      <c r="I84" t="s">
+        <v>15</v>
+      </c>
+      <c r="J84" t="s">
+        <v>15</v>
+      </c>
+      <c r="K84" t="s">
         <v>259</v>
-      </c>
-      <c r="H84" t="s">
-        <v>15</v>
-      </c>
-      <c r="I84" t="s">
-        <v>15</v>
-      </c>
-      <c r="J84" t="s">
-        <v>15</v>
-      </c>
-      <c r="K84" t="s">
-        <v>260</v>
       </c>
       <c r="L84" t="s">
         <v>193</v>
@@ -5956,7 +5953,7 @@
     </row>
     <row r="85" ht="70.5" spans="1:12">
       <c r="A85" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B85" t="s">
         <v>28</v>
@@ -5974,7 +5971,7 @@
         <v>15</v>
       </c>
       <c r="G85" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="H85" t="s">
         <v>15</v>
@@ -5994,7 +5991,7 @@
     </row>
     <row r="86" ht="55.5" spans="1:12">
       <c r="A86" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B86" t="s">
         <v>13</v>
@@ -6012,7 +6009,7 @@
         <v>15</v>
       </c>
       <c r="G86" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="H86" t="s">
         <v>15</v>
@@ -6032,7 +6029,7 @@
     </row>
     <row r="87" ht="40.5" spans="1:12">
       <c r="A87" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B87" t="s">
         <v>13</v>
@@ -6050,7 +6047,7 @@
         <v>15</v>
       </c>
       <c r="G87" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="H87" t="s">
         <v>15</v>
@@ -6070,7 +6067,7 @@
     </row>
     <row r="88" ht="69" spans="1:12">
       <c r="A88" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B88" t="s">
         <v>28</v>
@@ -6088,7 +6085,7 @@
         <v>15</v>
       </c>
       <c r="G88" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H88" t="s">
         <v>15</v>
@@ -6108,7 +6105,7 @@
     </row>
     <row r="89" ht="30" spans="1:12">
       <c r="A89" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B89" t="s">
         <v>13</v>
@@ -6126,27 +6123,27 @@
         <v>15</v>
       </c>
       <c r="G89" t="s">
+        <v>269</v>
+      </c>
+      <c r="H89" t="s">
+        <v>15</v>
+      </c>
+      <c r="I89" t="s">
+        <v>15</v>
+      </c>
+      <c r="J89" t="s">
+        <v>15</v>
+      </c>
+      <c r="K89" t="s">
+        <v>15</v>
+      </c>
+      <c r="L89" t="s">
         <v>270</v>
-      </c>
-      <c r="H89" t="s">
-        <v>15</v>
-      </c>
-      <c r="I89" t="s">
-        <v>15</v>
-      </c>
-      <c r="J89" t="s">
-        <v>15</v>
-      </c>
-      <c r="K89" t="s">
-        <v>15</v>
-      </c>
-      <c r="L89" t="s">
-        <v>271</v>
       </c>
     </row>
     <row r="90" ht="43.5" spans="1:12">
       <c r="A90" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B90" t="s">
         <v>28</v>
@@ -6164,27 +6161,27 @@
         <v>15</v>
       </c>
       <c r="G90" t="s">
+        <v>272</v>
+      </c>
+      <c r="H90" t="s">
+        <v>15</v>
+      </c>
+      <c r="I90" t="s">
+        <v>15</v>
+      </c>
+      <c r="J90" t="s">
+        <v>15</v>
+      </c>
+      <c r="K90" t="s">
+        <v>15</v>
+      </c>
+      <c r="L90" t="s">
         <v>273</v>
-      </c>
-      <c r="H90" t="s">
-        <v>15</v>
-      </c>
-      <c r="I90" t="s">
-        <v>15</v>
-      </c>
-      <c r="J90" t="s">
-        <v>15</v>
-      </c>
-      <c r="K90" t="s">
-        <v>15</v>
-      </c>
-      <c r="L90" t="s">
-        <v>274</v>
       </c>
     </row>
     <row r="91" ht="30" spans="1:12">
       <c r="A91" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B91" t="s">
         <v>28</v>
@@ -6202,7 +6199,7 @@
         <v>15</v>
       </c>
       <c r="G91" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H91" t="s">
         <v>15</v>
@@ -6222,7 +6219,7 @@
     </row>
     <row r="92" ht="30" spans="1:12">
       <c r="A92" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B92" t="s">
         <v>13</v>
@@ -6240,7 +6237,7 @@
         <v>15</v>
       </c>
       <c r="G92" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H92" t="s">
         <v>15</v>
@@ -6255,12 +6252,12 @@
         <v>35</v>
       </c>
       <c r="L92" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="93" ht="40.5" spans="1:12">
       <c r="A93" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B93" t="s">
         <v>13</v>
@@ -6275,7 +6272,7 @@
         <v>15</v>
       </c>
       <c r="G93" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="H93" t="s">
         <v>15</v>
@@ -6292,7 +6289,7 @@
     </row>
     <row r="94" spans="1:12">
       <c r="A94" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B94" t="s">
         <v>108</v>
@@ -6310,27 +6307,27 @@
         <v>15</v>
       </c>
       <c r="G94" t="s">
+        <v>282</v>
+      </c>
+      <c r="H94" t="s">
+        <v>15</v>
+      </c>
+      <c r="I94" t="s">
+        <v>15</v>
+      </c>
+      <c r="J94" t="s">
+        <v>15</v>
+      </c>
+      <c r="K94" t="s">
+        <v>15</v>
+      </c>
+      <c r="L94" t="s">
         <v>283</v>
-      </c>
-      <c r="H94" t="s">
-        <v>15</v>
-      </c>
-      <c r="I94" t="s">
-        <v>15</v>
-      </c>
-      <c r="J94" t="s">
-        <v>15</v>
-      </c>
-      <c r="K94" t="s">
-        <v>15</v>
-      </c>
-      <c r="L94" t="s">
-        <v>284</v>
       </c>
     </row>
     <row r="95" ht="40.5" spans="1:12">
       <c r="A95" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B95" t="s">
         <v>13</v>
@@ -6348,27 +6345,27 @@
         <v>15</v>
       </c>
       <c r="G95" t="s">
+        <v>285</v>
+      </c>
+      <c r="H95" t="s">
+        <v>15</v>
+      </c>
+      <c r="I95" t="s">
+        <v>15</v>
+      </c>
+      <c r="J95" t="s">
+        <v>15</v>
+      </c>
+      <c r="K95" t="s">
+        <v>15</v>
+      </c>
+      <c r="L95" t="s">
         <v>286</v>
-      </c>
-      <c r="H95" t="s">
-        <v>15</v>
-      </c>
-      <c r="I95" t="s">
-        <v>15</v>
-      </c>
-      <c r="J95" t="s">
-        <v>15</v>
-      </c>
-      <c r="K95" t="s">
-        <v>15</v>
-      </c>
-      <c r="L95" t="s">
-        <v>287</v>
       </c>
     </row>
     <row r="96" ht="40.5" spans="1:12">
       <c r="A96" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B96" t="s">
         <v>108</v>
@@ -6386,27 +6383,27 @@
         <v>15</v>
       </c>
       <c r="G96" t="s">
+        <v>288</v>
+      </c>
+      <c r="H96" t="s">
+        <v>15</v>
+      </c>
+      <c r="I96" t="s">
+        <v>15</v>
+      </c>
+      <c r="J96" t="s">
+        <v>15</v>
+      </c>
+      <c r="K96" t="s">
+        <v>15</v>
+      </c>
+      <c r="L96" t="s">
         <v>289</v>
-      </c>
-      <c r="H96" t="s">
-        <v>15</v>
-      </c>
-      <c r="I96" t="s">
-        <v>15</v>
-      </c>
-      <c r="J96" t="s">
-        <v>15</v>
-      </c>
-      <c r="K96" t="s">
-        <v>15</v>
-      </c>
-      <c r="L96" t="s">
-        <v>290</v>
       </c>
     </row>
     <row r="97" ht="40.5" spans="1:12">
       <c r="A97" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B97" t="s">
         <v>13</v>
@@ -6424,27 +6421,27 @@
         <v>15</v>
       </c>
       <c r="G97" t="s">
+        <v>291</v>
+      </c>
+      <c r="H97" t="s">
+        <v>15</v>
+      </c>
+      <c r="I97" t="s">
+        <v>15</v>
+      </c>
+      <c r="J97" t="s">
+        <v>15</v>
+      </c>
+      <c r="K97" t="s">
+        <v>15</v>
+      </c>
+      <c r="L97" t="s">
         <v>292</v>
-      </c>
-      <c r="H97" t="s">
-        <v>15</v>
-      </c>
-      <c r="I97" t="s">
-        <v>15</v>
-      </c>
-      <c r="J97" t="s">
-        <v>15</v>
-      </c>
-      <c r="K97" t="s">
-        <v>15</v>
-      </c>
-      <c r="L97" t="s">
-        <v>293</v>
       </c>
     </row>
     <row r="98" ht="40.5" spans="1:12">
       <c r="A98" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B98" t="s">
         <v>28</v>
@@ -6462,7 +6459,7 @@
         <v>15</v>
       </c>
       <c r="G98" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H98" t="s">
         <v>15</v>
@@ -6477,12 +6474,12 @@
         <v>31</v>
       </c>
       <c r="L98" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="99" ht="40.5" spans="1:12">
       <c r="A99" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="B99" t="s">
         <v>13</v>
@@ -6500,7 +6497,7 @@
         <v>15</v>
       </c>
       <c r="G99" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="H99" t="s">
         <v>15</v>
@@ -6520,7 +6517,7 @@
     </row>
     <row r="100" ht="30" spans="1:12">
       <c r="A100" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="B100" t="s">
         <v>28</v>
@@ -6538,27 +6535,27 @@
         <v>15</v>
       </c>
       <c r="G100" t="s">
+        <v>299</v>
+      </c>
+      <c r="H100" t="s">
+        <v>15</v>
+      </c>
+      <c r="I100" t="s">
+        <v>15</v>
+      </c>
+      <c r="J100" t="s">
+        <v>15</v>
+      </c>
+      <c r="K100" t="s">
+        <v>15</v>
+      </c>
+      <c r="L100" t="s">
         <v>300</v>
-      </c>
-      <c r="H100" t="s">
-        <v>15</v>
-      </c>
-      <c r="I100" t="s">
-        <v>15</v>
-      </c>
-      <c r="J100" t="s">
-        <v>15</v>
-      </c>
-      <c r="K100" t="s">
-        <v>15</v>
-      </c>
-      <c r="L100" t="s">
-        <v>301</v>
       </c>
     </row>
     <row r="101" ht="30" spans="1:12">
       <c r="A101" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B101" t="s">
         <v>28</v>
@@ -6576,27 +6573,27 @@
         <v>15</v>
       </c>
       <c r="G101" t="s">
+        <v>302</v>
+      </c>
+      <c r="H101" t="s">
+        <v>15</v>
+      </c>
+      <c r="I101" t="s">
+        <v>15</v>
+      </c>
+      <c r="J101" t="s">
+        <v>15</v>
+      </c>
+      <c r="K101" t="s">
+        <v>15</v>
+      </c>
+      <c r="L101" t="s">
         <v>303</v>
-      </c>
-      <c r="H101" t="s">
-        <v>15</v>
-      </c>
-      <c r="I101" t="s">
-        <v>15</v>
-      </c>
-      <c r="J101" t="s">
-        <v>15</v>
-      </c>
-      <c r="K101" t="s">
-        <v>15</v>
-      </c>
-      <c r="L101" t="s">
-        <v>304</v>
       </c>
     </row>
     <row r="102" ht="40.5" spans="1:12">
       <c r="A102" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B102" t="s">
         <v>13</v>
@@ -6614,27 +6611,27 @@
         <v>15</v>
       </c>
       <c r="G102" t="s">
+        <v>305</v>
+      </c>
+      <c r="H102" t="s">
+        <v>15</v>
+      </c>
+      <c r="I102" t="s">
+        <v>15</v>
+      </c>
+      <c r="J102" t="s">
+        <v>15</v>
+      </c>
+      <c r="K102" t="s">
+        <v>15</v>
+      </c>
+      <c r="L102" t="s">
         <v>306</v>
-      </c>
-      <c r="H102" t="s">
-        <v>15</v>
-      </c>
-      <c r="I102" t="s">
-        <v>15</v>
-      </c>
-      <c r="J102" t="s">
-        <v>15</v>
-      </c>
-      <c r="K102" t="s">
-        <v>15</v>
-      </c>
-      <c r="L102" t="s">
-        <v>307</v>
       </c>
     </row>
     <row r="103" ht="55.5" spans="1:12">
       <c r="A103" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B103" t="s">
         <v>28</v>
@@ -6652,27 +6649,27 @@
         <v>15</v>
       </c>
       <c r="G103" t="s">
+        <v>308</v>
+      </c>
+      <c r="H103" t="s">
+        <v>15</v>
+      </c>
+      <c r="I103" t="s">
+        <v>15</v>
+      </c>
+      <c r="J103" t="s">
+        <v>15</v>
+      </c>
+      <c r="K103" t="s">
+        <v>15</v>
+      </c>
+      <c r="L103" t="s">
         <v>309</v>
-      </c>
-      <c r="H103" t="s">
-        <v>15</v>
-      </c>
-      <c r="I103" t="s">
-        <v>15</v>
-      </c>
-      <c r="J103" t="s">
-        <v>15</v>
-      </c>
-      <c r="K103" t="s">
-        <v>15</v>
-      </c>
-      <c r="L103" t="s">
-        <v>310</v>
       </c>
     </row>
     <row r="104" ht="40.5" spans="1:12">
       <c r="A104" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B104" t="s">
         <v>13</v>
@@ -6690,27 +6687,27 @@
         <v>15</v>
       </c>
       <c r="G104" t="s">
+        <v>311</v>
+      </c>
+      <c r="H104" t="s">
+        <v>15</v>
+      </c>
+      <c r="I104" t="s">
+        <v>15</v>
+      </c>
+      <c r="J104" t="s">
+        <v>15</v>
+      </c>
+      <c r="K104" t="s">
+        <v>15</v>
+      </c>
+      <c r="L104" t="s">
         <v>312</v>
-      </c>
-      <c r="H104" t="s">
-        <v>15</v>
-      </c>
-      <c r="I104" t="s">
-        <v>15</v>
-      </c>
-      <c r="J104" t="s">
-        <v>15</v>
-      </c>
-      <c r="K104" t="s">
-        <v>15</v>
-      </c>
-      <c r="L104" t="s">
-        <v>313</v>
       </c>
     </row>
     <row r="105" ht="67.5" spans="1:12">
       <c r="A105" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B105" t="s">
         <v>28</v>
@@ -6728,22 +6725,22 @@
         <v>15</v>
       </c>
       <c r="G105" t="s">
+        <v>314</v>
+      </c>
+      <c r="H105" t="s">
+        <v>15</v>
+      </c>
+      <c r="I105" t="s">
+        <v>15</v>
+      </c>
+      <c r="J105" t="s">
+        <v>15</v>
+      </c>
+      <c r="K105" s="2" t="s">
         <v>315</v>
       </c>
-      <c r="H105" t="s">
-        <v>15</v>
-      </c>
-      <c r="I105" t="s">
-        <v>15</v>
-      </c>
-      <c r="J105" t="s">
-        <v>15</v>
-      </c>
-      <c r="K105" s="2" t="s">
+      <c r="L105" t="s">
         <v>316</v>
-      </c>
-      <c r="L105" t="s">
-        <v>317</v>
       </c>
     </row>
   </sheetData>
@@ -6764,47 +6761,47 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>318</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>319</v>
       </c>
     </row>
     <row r="2" ht="30" spans="1:2">
       <c r="A2" t="s">
+        <v>319</v>
+      </c>
+      <c r="B2" t="s">
         <v>320</v>
-      </c>
-      <c r="B2" t="s">
-        <v>321</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
+        <v>321</v>
+      </c>
+      <c r="B3" t="s">
         <v>322</v>
-      </c>
-      <c r="B3" t="s">
-        <v>323</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B4" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
+        <v>324</v>
+      </c>
+      <c r="B5" t="s">
         <v>325</v>
-      </c>
-      <c r="B5" t="s">
-        <v>326</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B6" t="s">
         <v>157</v>
@@ -6812,7 +6809,7 @@
     </row>
     <row r="7" ht="27" spans="1:2">
       <c r="A7" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B7" t="s">
         <v>18</v>
@@ -6820,7 +6817,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B8" t="s">
         <v>217</v>
@@ -6828,7 +6825,7 @@
     </row>
     <row r="9" ht="27" spans="1:2">
       <c r="A9" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B9" t="s">
         <v>202</v>
@@ -6836,50 +6833,50 @@
     </row>
     <row r="10" ht="75" spans="1:2">
       <c r="A10" t="s">
+        <v>330</v>
+      </c>
+      <c r="B10" t="s">
         <v>331</v>
-      </c>
-      <c r="B10" t="s">
-        <v>332</v>
       </c>
     </row>
     <row r="11" ht="75" spans="1:2">
       <c r="A11" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B11" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="12" ht="57" spans="1:2">
       <c r="A12" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B12" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="13" ht="58.5" spans="1:2">
       <c r="A13" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B13" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="14" ht="60" spans="1:2">
       <c r="A14" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B14" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="15" ht="75" spans="1:2">
       <c r="A15" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B15" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
   </sheetData>
@@ -6901,616 +6898,616 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>338</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>339</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>340</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>341</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>342</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>343</v>
       </c>
     </row>
     <row r="2" ht="73.5" spans="1:6">
       <c r="A2" t="s">
+        <v>343</v>
+      </c>
+      <c r="B2" t="s">
         <v>344</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>345</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>346</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>347</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>348</v>
-      </c>
-      <c r="F2" t="s">
-        <v>349</v>
       </c>
     </row>
     <row r="3" ht="103.5" spans="1:6">
       <c r="A3" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="B3" t="s">
+        <v>349</v>
+      </c>
+      <c r="C3" t="s">
         <v>350</v>
       </c>
-      <c r="C3" t="s">
+      <c r="D3" t="s">
         <v>351</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" t="s">
         <v>352</v>
       </c>
-      <c r="E3" t="s">
+      <c r="F3" t="s">
         <v>353</v>
-      </c>
-      <c r="F3" t="s">
-        <v>354</v>
       </c>
     </row>
     <row r="4" ht="45" spans="1:6">
       <c r="A4" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="B4" t="s">
+        <v>354</v>
+      </c>
+      <c r="C4" t="s">
         <v>355</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" t="s">
         <v>356</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E4" t="s">
         <v>357</v>
       </c>
-      <c r="E4" t="s">
+      <c r="F4" t="s">
         <v>358</v>
-      </c>
-      <c r="F4" t="s">
-        <v>359</v>
       </c>
     </row>
     <row r="5" ht="45" spans="1:6">
       <c r="A5" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="B5" t="s">
+        <v>359</v>
+      </c>
+      <c r="C5" t="s">
         <v>360</v>
       </c>
-      <c r="C5" t="s">
+      <c r="D5" t="s">
         <v>361</v>
       </c>
-      <c r="D5" t="s">
+      <c r="E5" t="s">
         <v>362</v>
       </c>
-      <c r="E5" t="s">
+      <c r="F5" t="s">
         <v>363</v>
-      </c>
-      <c r="F5" t="s">
-        <v>364</v>
       </c>
     </row>
     <row r="6" ht="45" spans="1:6">
       <c r="A6" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="B6" t="s">
+        <v>364</v>
+      </c>
+      <c r="C6" t="s">
         <v>365</v>
       </c>
-      <c r="C6" t="s">
+      <c r="D6" t="s">
         <v>366</v>
       </c>
-      <c r="D6" t="s">
+      <c r="E6" t="s">
         <v>367</v>
       </c>
-      <c r="E6" t="s">
+      <c r="F6" t="s">
         <v>368</v>
-      </c>
-      <c r="F6" t="s">
-        <v>369</v>
       </c>
     </row>
     <row r="7" ht="75" spans="1:6">
       <c r="A7" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="B7" t="s">
+        <v>369</v>
+      </c>
+      <c r="C7" t="s">
         <v>370</v>
       </c>
-      <c r="C7" t="s">
+      <c r="D7" t="s">
         <v>371</v>
       </c>
-      <c r="D7" t="s">
+      <c r="E7" t="s">
         <v>372</v>
       </c>
-      <c r="E7" t="s">
+      <c r="F7" t="s">
         <v>373</v>
-      </c>
-      <c r="F7" t="s">
-        <v>374</v>
       </c>
     </row>
     <row r="8" ht="45" spans="1:6">
       <c r="A8" t="s">
+        <v>374</v>
+      </c>
+      <c r="B8" t="s">
         <v>375</v>
       </c>
-      <c r="B8" t="s">
+      <c r="C8" t="s">
         <v>376</v>
       </c>
-      <c r="C8" t="s">
+      <c r="D8" t="s">
         <v>377</v>
       </c>
-      <c r="D8" t="s">
+      <c r="E8" t="s">
         <v>378</v>
       </c>
-      <c r="E8" t="s">
+      <c r="F8" t="s">
         <v>379</v>
-      </c>
-      <c r="F8" t="s">
-        <v>380</v>
       </c>
     </row>
     <row r="9" ht="45" spans="1:6">
       <c r="A9" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="B9" t="s">
+        <v>380</v>
+      </c>
+      <c r="C9" t="s">
         <v>381</v>
       </c>
-      <c r="C9" t="s">
+      <c r="D9" t="s">
         <v>382</v>
       </c>
-      <c r="D9" t="s">
+      <c r="E9" t="s">
         <v>383</v>
       </c>
-      <c r="E9" t="s">
+      <c r="F9" t="s">
         <v>384</v>
-      </c>
-      <c r="F9" t="s">
-        <v>385</v>
       </c>
     </row>
     <row r="10" ht="58.5" spans="1:6">
       <c r="A10" t="s">
+        <v>385</v>
+      </c>
+      <c r="B10" t="s">
         <v>386</v>
       </c>
-      <c r="B10" t="s">
+      <c r="C10" t="s">
         <v>387</v>
       </c>
-      <c r="C10" t="s">
+      <c r="D10" t="s">
         <v>388</v>
       </c>
-      <c r="D10" t="s">
+      <c r="E10" t="s">
         <v>389</v>
       </c>
-      <c r="E10" t="s">
+      <c r="F10" t="s">
         <v>390</v>
-      </c>
-      <c r="F10" t="s">
-        <v>391</v>
       </c>
     </row>
     <row r="11" ht="60" spans="1:6">
       <c r="A11" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="B11" t="s">
+        <v>391</v>
+      </c>
+      <c r="C11" t="s">
         <v>392</v>
       </c>
-      <c r="C11" t="s">
+      <c r="D11" t="s">
         <v>393</v>
       </c>
-      <c r="D11" t="s">
+      <c r="E11" t="s">
         <v>394</v>
       </c>
-      <c r="E11" t="s">
+      <c r="F11" t="s">
         <v>395</v>
-      </c>
-      <c r="F11" t="s">
-        <v>396</v>
       </c>
     </row>
     <row r="12" ht="58.5" spans="1:6">
       <c r="A12" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="B12" t="s">
+        <v>396</v>
+      </c>
+      <c r="C12" t="s">
         <v>397</v>
       </c>
-      <c r="C12" t="s">
+      <c r="D12" t="s">
         <v>398</v>
       </c>
-      <c r="D12" t="s">
+      <c r="E12" t="s">
         <v>399</v>
       </c>
-      <c r="E12" t="s">
+      <c r="F12" t="s">
         <v>400</v>
-      </c>
-      <c r="F12" t="s">
-        <v>401</v>
       </c>
     </row>
     <row r="13" ht="58.5" spans="1:6">
       <c r="A13" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="B13" t="s">
+        <v>401</v>
+      </c>
+      <c r="C13" t="s">
         <v>402</v>
       </c>
-      <c r="C13" t="s">
+      <c r="D13" t="s">
         <v>403</v>
       </c>
-      <c r="D13" t="s">
+      <c r="E13" t="s">
         <v>404</v>
       </c>
-      <c r="E13" t="s">
+      <c r="F13" t="s">
         <v>405</v>
-      </c>
-      <c r="F13" t="s">
-        <v>406</v>
       </c>
     </row>
     <row r="14" ht="58.5" spans="1:6">
       <c r="A14" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="B14" t="s">
+        <v>406</v>
+      </c>
+      <c r="C14" t="s">
         <v>407</v>
       </c>
-      <c r="C14" t="s">
+      <c r="D14" t="s">
         <v>408</v>
       </c>
-      <c r="D14" t="s">
+      <c r="E14" t="s">
         <v>409</v>
       </c>
-      <c r="E14" t="s">
+      <c r="F14" t="s">
         <v>410</v>
-      </c>
-      <c r="F14" t="s">
-        <v>411</v>
       </c>
     </row>
     <row r="15" ht="58.5" spans="1:6">
       <c r="A15" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="B15" t="s">
+        <v>411</v>
+      </c>
+      <c r="C15" t="s">
         <v>412</v>
       </c>
-      <c r="C15" t="s">
+      <c r="D15" t="s">
         <v>413</v>
       </c>
-      <c r="D15" t="s">
+      <c r="E15" t="s">
         <v>414</v>
       </c>
-      <c r="E15" t="s">
+      <c r="F15" t="s">
         <v>415</v>
-      </c>
-      <c r="F15" t="s">
-        <v>416</v>
       </c>
     </row>
     <row r="16" ht="58.5" spans="1:6">
       <c r="A16" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="B16" t="s">
+        <v>416</v>
+      </c>
+      <c r="C16" t="s">
         <v>417</v>
       </c>
-      <c r="C16" t="s">
+      <c r="D16" t="s">
         <v>418</v>
       </c>
-      <c r="D16" t="s">
+      <c r="E16" t="s">
         <v>419</v>
       </c>
-      <c r="E16" t="s">
+      <c r="F16" t="s">
         <v>420</v>
-      </c>
-      <c r="F16" t="s">
-        <v>421</v>
       </c>
     </row>
     <row r="17" ht="58.5" spans="1:6">
       <c r="A17" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="B17" t="s">
+        <v>421</v>
+      </c>
+      <c r="C17" t="s">
         <v>422</v>
       </c>
-      <c r="C17" t="s">
+      <c r="D17" t="s">
         <v>423</v>
       </c>
-      <c r="D17" t="s">
+      <c r="E17" t="s">
         <v>424</v>
       </c>
-      <c r="E17" t="s">
+      <c r="F17" t="s">
         <v>425</v>
-      </c>
-      <c r="F17" t="s">
-        <v>426</v>
       </c>
     </row>
     <row r="18" ht="58.5" spans="1:6">
       <c r="A18" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="B18" t="s">
+        <v>426</v>
+      </c>
+      <c r="C18" t="s">
         <v>427</v>
       </c>
-      <c r="C18" t="s">
+      <c r="D18" t="s">
         <v>428</v>
       </c>
-      <c r="D18" t="s">
+      <c r="E18" t="s">
         <v>429</v>
       </c>
-      <c r="E18" t="s">
+      <c r="F18" t="s">
         <v>430</v>
-      </c>
-      <c r="F18" t="s">
-        <v>431</v>
       </c>
     </row>
     <row r="19" ht="58.5" spans="1:6">
       <c r="A19" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="B19" t="s">
+        <v>431</v>
+      </c>
+      <c r="C19" t="s">
         <v>432</v>
       </c>
-      <c r="C19" t="s">
+      <c r="D19" t="s">
         <v>433</v>
       </c>
-      <c r="D19" t="s">
+      <c r="E19" t="s">
         <v>434</v>
       </c>
-      <c r="E19" t="s">
+      <c r="F19" t="s">
         <v>435</v>
-      </c>
-      <c r="F19" t="s">
-        <v>436</v>
       </c>
     </row>
     <row r="20" ht="72" spans="1:6">
       <c r="A20" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="B20" t="s">
+        <v>436</v>
+      </c>
+      <c r="C20" t="s">
         <v>437</v>
       </c>
-      <c r="C20" t="s">
+      <c r="D20" t="s">
         <v>438</v>
       </c>
-      <c r="D20" t="s">
+      <c r="E20" t="s">
         <v>439</v>
       </c>
-      <c r="E20" t="s">
+      <c r="F20" t="s">
         <v>440</v>
-      </c>
-      <c r="F20" t="s">
-        <v>441</v>
       </c>
     </row>
     <row r="21" ht="58.5" spans="1:6">
       <c r="A21" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="B21" t="s">
+        <v>441</v>
+      </c>
+      <c r="C21" t="s">
         <v>442</v>
       </c>
-      <c r="C21" t="s">
+      <c r="D21" t="s">
         <v>443</v>
       </c>
-      <c r="D21" t="s">
+      <c r="E21" t="s">
         <v>444</v>
       </c>
-      <c r="E21" t="s">
+      <c r="F21" t="s">
         <v>445</v>
-      </c>
-      <c r="F21" t="s">
-        <v>446</v>
       </c>
     </row>
     <row r="22" ht="58.5" spans="1:6">
       <c r="A22" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="B22" t="s">
+        <v>446</v>
+      </c>
+      <c r="C22" t="s">
         <v>447</v>
       </c>
-      <c r="C22" t="s">
+      <c r="D22" t="s">
         <v>448</v>
       </c>
-      <c r="D22" t="s">
+      <c r="E22" t="s">
         <v>449</v>
       </c>
-      <c r="E22" t="s">
+      <c r="F22" t="s">
         <v>450</v>
-      </c>
-      <c r="F22" t="s">
-        <v>451</v>
       </c>
     </row>
     <row r="23" ht="58.5" spans="1:6">
       <c r="A23" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="B23" t="s">
+        <v>451</v>
+      </c>
+      <c r="C23" t="s">
         <v>452</v>
       </c>
-      <c r="C23" t="s">
+      <c r="D23" t="s">
         <v>453</v>
       </c>
-      <c r="D23" t="s">
+      <c r="E23" t="s">
         <v>454</v>
       </c>
-      <c r="E23" t="s">
+      <c r="F23" t="s">
         <v>455</v>
-      </c>
-      <c r="F23" t="s">
-        <v>456</v>
       </c>
     </row>
     <row r="24" ht="58.5" spans="1:6">
       <c r="A24" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="B24" t="s">
+        <v>456</v>
+      </c>
+      <c r="C24" t="s">
         <v>457</v>
       </c>
-      <c r="C24" t="s">
+      <c r="D24" t="s">
+        <v>398</v>
+      </c>
+      <c r="E24" t="s">
         <v>458</v>
       </c>
-      <c r="D24" t="s">
-        <v>399</v>
-      </c>
-      <c r="E24" t="s">
+      <c r="F24" t="s">
         <v>459</v>
-      </c>
-      <c r="F24" t="s">
-        <v>460</v>
       </c>
     </row>
     <row r="25" ht="90" spans="1:6">
       <c r="A25" t="s">
+        <v>460</v>
+      </c>
+      <c r="B25" t="s">
         <v>461</v>
       </c>
-      <c r="B25" t="s">
+      <c r="C25" t="s">
         <v>462</v>
       </c>
-      <c r="C25" t="s">
+      <c r="D25" t="s">
         <v>463</v>
       </c>
-      <c r="D25" t="s">
+      <c r="E25" t="s">
         <v>464</v>
       </c>
-      <c r="E25" t="s">
+      <c r="F25" t="s">
         <v>465</v>
-      </c>
-      <c r="F25" t="s">
-        <v>466</v>
       </c>
     </row>
     <row r="26" ht="58.5" spans="1:6">
       <c r="A26" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="B26" t="s">
+        <v>466</v>
+      </c>
+      <c r="C26" t="s">
         <v>467</v>
       </c>
-      <c r="C26" t="s">
+      <c r="D26" t="s">
         <v>468</v>
       </c>
-      <c r="D26" t="s">
+      <c r="E26" t="s">
         <v>469</v>
       </c>
-      <c r="E26" t="s">
+      <c r="F26" t="s">
         <v>470</v>
-      </c>
-      <c r="F26" t="s">
-        <v>471</v>
       </c>
     </row>
     <row r="27" ht="58.5" spans="1:6">
       <c r="A27" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="B27" t="s">
+        <v>471</v>
+      </c>
+      <c r="C27" t="s">
         <v>472</v>
       </c>
-      <c r="C27" t="s">
+      <c r="D27" t="s">
         <v>473</v>
       </c>
-      <c r="D27" t="s">
+      <c r="E27" t="s">
         <v>474</v>
       </c>
-      <c r="E27" t="s">
+      <c r="F27" t="s">
         <v>475</v>
-      </c>
-      <c r="F27" t="s">
-        <v>476</v>
       </c>
     </row>
     <row r="28" ht="58.5" spans="1:6">
       <c r="A28" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="B28" t="s">
+        <v>476</v>
+      </c>
+      <c r="C28" t="s">
         <v>477</v>
       </c>
-      <c r="C28" t="s">
+      <c r="D28" t="s">
+        <v>473</v>
+      </c>
+      <c r="E28" t="s">
         <v>478</v>
       </c>
-      <c r="D28" t="s">
-        <v>474</v>
-      </c>
-      <c r="E28" t="s">
+      <c r="F28" t="s">
         <v>479</v>
-      </c>
-      <c r="F28" t="s">
-        <v>480</v>
       </c>
     </row>
     <row r="29" ht="73.5" spans="1:6">
       <c r="A29" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="B29" t="s">
+        <v>480</v>
+      </c>
+      <c r="C29" t="s">
         <v>481</v>
       </c>
-      <c r="C29" t="s">
+      <c r="D29" t="s">
         <v>482</v>
       </c>
-      <c r="D29" t="s">
+      <c r="E29" t="s">
         <v>483</v>
       </c>
-      <c r="E29" t="s">
+      <c r="F29" t="s">
         <v>484</v>
-      </c>
-      <c r="F29" t="s">
-        <v>485</v>
       </c>
     </row>
     <row r="30" ht="58.5" spans="1:6">
       <c r="A30" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="B30" t="s">
+        <v>485</v>
+      </c>
+      <c r="C30" t="s">
         <v>486</v>
       </c>
-      <c r="C30" t="s">
+      <c r="D30" t="s">
         <v>487</v>
       </c>
-      <c r="D30" t="s">
+      <c r="E30" t="s">
         <v>488</v>
       </c>
-      <c r="E30" t="s">
+      <c r="F30" t="s">
         <v>489</v>
-      </c>
-      <c r="F30" t="s">
-        <v>490</v>
       </c>
     </row>
     <row r="31" spans="1:6">
       <c r="A31" t="s">
+        <v>490</v>
+      </c>
+      <c r="B31" t="s">
         <v>491</v>
       </c>
-      <c r="B31" t="s">
+      <c r="C31" t="s">
         <v>492</v>
       </c>
-      <c r="C31" t="s">
+      <c r="D31" t="s">
         <v>493</v>
-      </c>
-      <c r="D31" t="s">
-        <v>494</v>
       </c>
     </row>
   </sheetData>
